--- a/data/Migration.xlsx
+++ b/data/Migration.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Apache24\htdocs\robotv3\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{245F6232-788B-4A07-B432-373C9F9E9072}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F6C79D6-3778-4A63-A459-AE1130AE9615}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9662A57A-0758-4128-97DC-382A9DB98F6F}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{9662A57A-0758-4128-97DC-382A9DB98F6F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -987,11 +987,11 @@
       </c>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="I9">
         <f t="shared" ref="I9:I77" si="1">IF(OR(C9="OK",C9="-"),1,0)</f>
@@ -2081,11 +2081,11 @@
       </c>
     </row>
     <row r="65" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B65" s="18" t="s">
+      <c r="B65" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="I65">
         <f t="shared" si="1"/>
